--- a/experiment_data.xlsx
+++ b/experiment_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhc/Documents/PhD/projects/VerbalTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{49A8121B-CB46-1C42-9EA6-BEF7E960F646}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB336919-649D-9F4F-A0EB-B6F2B2ABC7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5180" yWindow="1800" windowWidth="28040" windowHeight="17440" xr2:uid="{D54BE283-3255-1641-9B34-5AB1125DFA56}"/>
+    <workbookView xWindow="14760" yWindow="2700" windowWidth="28040" windowHeight="17440" xr2:uid="{D54BE283-3255-1641-9B34-5AB1125DFA56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,15 +35,92 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+  <si>
+    <t>Synthetic U</t>
+  </si>
+  <si>
+    <t>Synthetic M</t>
+  </si>
+  <si>
+    <t>Istanbul</t>
+  </si>
+  <si>
+    <t>unconditional ablation</t>
+  </si>
+  <si>
+    <t>Disc</t>
+  </si>
+  <si>
+    <t>Pred</t>
+  </si>
+  <si>
+    <t>FID</t>
+  </si>
+  <si>
+    <t>0.0975 +- 0.0082</t>
+  </si>
+  <si>
+    <t>0.0817+- 0.0081</t>
+  </si>
+  <si>
+    <t>qwen+naïve aggregate+real text</t>
+  </si>
+  <si>
+    <t>qwen+naïve aggregate + fake text</t>
+  </si>
+  <si>
+    <t>0.0615+=0.0128</t>
+  </si>
+  <si>
+    <t>verbalTS original</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verbalTS caption naïve aggregate </t>
+  </si>
+  <si>
+    <t>0.1732+-0.0252</t>
+  </si>
+  <si>
+    <t>0.1849+-0.0270</t>
+  </si>
+  <si>
+    <t>0.1768+-0.0186</t>
+  </si>
+  <si>
+    <t>0.1540+-0.0089</t>
+  </si>
+  <si>
+    <t>0.0861+-0.0158</t>
+  </si>
+  <si>
+    <t>0.2400+-0.0051</t>
+  </si>
+  <si>
+    <t>0.2427+-0.0031</t>
+  </si>
+  <si>
+    <t>0.2445+-0.0047</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="27"/>
+      <color rgb="FF000000"/>
+      <name val="Menlo"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -66,8 +143,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,9 +480,124 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78B2F557-2458-4144-BF20-A2AABD55101C}">
-  <dimension ref="A1"/>
+  <dimension ref="F6:L19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <cols>
+    <col min="8" max="8" width="29.1640625" customWidth="1"/>
+    <col min="9" max="9" width="27.5" customWidth="1"/>
+    <col min="10" max="10" width="20.83203125" customWidth="1"/>
+    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="12" max="12" width="20.33203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="6" spans="6:12" ht="34" x14ac:dyDescent="0.35">
+      <c r="H6" s="1"/>
+    </row>
+    <row r="8" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="H8" t="s">
+        <v>10</v>
+      </c>
+      <c r="I8" t="s">
+        <v>9</v>
+      </c>
+      <c r="J8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K8" t="s">
+        <v>13</v>
+      </c>
+      <c r="L8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="F9" t="s">
+        <v>4</v>
+      </c>
+      <c r="G9" t="s">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" t="s">
+        <v>11</v>
+      </c>
+      <c r="K9" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="10" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="G10" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" t="s">
+        <v>19</v>
+      </c>
+      <c r="L10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="G11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="F13" t="s">
+        <v>5</v>
+      </c>
+      <c r="G13" t="s">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>15</v>
+      </c>
+      <c r="I13" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" t="s">
+        <v>17</v>
+      </c>
+      <c r="L13" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="14" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="G14" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="G15" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="F17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="G18" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="G19" t="s">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/experiment_data.xlsx
+++ b/experiment_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zhc/Documents/PhD/projects/VerbalTS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB336919-649D-9F4F-A0EB-B6F2B2ABC7AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAD61532-69E8-F242-9BDF-61C0C23E65A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14760" yWindow="2700" windowWidth="28040" windowHeight="17440" xr2:uid="{D54BE283-3255-1641-9B34-5AB1125DFA56}"/>
+    <workbookView xWindow="3320" yWindow="4020" windowWidth="28040" windowHeight="17440" xr2:uid="{D54BE283-3255-1641-9B34-5AB1125DFA56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="37">
   <si>
     <t>Synthetic U</t>
   </si>
@@ -77,9 +77,6 @@
     <t>verbalTS original</t>
   </si>
   <si>
-    <t xml:space="preserve">verbalTS caption naïve aggregate </t>
-  </si>
-  <si>
     <t>0.1732+-0.0252</t>
   </si>
   <si>
@@ -102,13 +99,61 @@
   </si>
   <si>
     <t>0.2445+-0.0047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">verbalTS caption+qwen+ naïve aggregate </t>
+  </si>
+  <si>
+    <t>useless</t>
+  </si>
+  <si>
+    <t>0.8084+-0.0232</t>
+  </si>
+  <si>
+    <t>0.5756 \pm 0.0252</t>
+  </si>
+  <si>
+    <t>0.5057 \pm 0.0233</t>
+  </si>
+  <si>
+    <t>KID</t>
+  </si>
+  <si>
+    <t>0.004541 \pm 0.000654</t>
+  </si>
+  <si>
+    <t>0.003651 \pm 0.000621</t>
+  </si>
+  <si>
+    <t>0.010371 \pm 0.000604</t>
+  </si>
+  <si>
+    <t>CMMD</t>
+  </si>
+  <si>
+    <t>0.000705 \pm 0.000001</t>
+  </si>
+  <si>
+    <t>0.000707 \pm 0.000001</t>
+  </si>
+  <si>
+    <t>0.000511 \pm 0.000000</t>
+  </si>
+  <si>
+    <t>0.5400 \pm 0.0185</t>
+  </si>
+  <si>
+    <t>0.5726 \pm 0.0262</t>
+  </si>
+  <si>
+    <t>0.8681 \pm 0.0238</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -122,13 +167,51 @@
       <name val="Menlo"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="36"/>
+      <color theme="1" tint="0.14999847407452621"/>
+      <name val="Aptos Narrow (Body)"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1" tint="0.14999847407452621"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1" tint="0.14999847407452621"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -143,9 +226,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -480,18 +572,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{78B2F557-2458-4144-BF20-A2AABD55101C}">
-  <dimension ref="F6:L19"/>
+  <dimension ref="F6:L27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="8" max="8" width="29.1640625" customWidth="1"/>
     <col min="9" max="9" width="27.5" customWidth="1"/>
     <col min="10" max="10" width="20.83203125" customWidth="1"/>
-    <col min="11" max="11" width="30" customWidth="1"/>
+    <col min="11" max="11" width="33.83203125" customWidth="1"/>
     <col min="12" max="12" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="6:12" ht="34" x14ac:dyDescent="0.35">
+    <row r="6" spans="6:12" ht="47" x14ac:dyDescent="0.55000000000000004">
       <c r="H6" s="1"/>
+      <c r="J6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K6" s="5"/>
+    </row>
+    <row r="7" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="J7" s="4"/>
+      <c r="K7" s="5"/>
     </row>
     <row r="8" spans="6:12" x14ac:dyDescent="0.2">
       <c r="H8" t="s">
@@ -500,11 +600,11 @@
       <c r="I8" t="s">
         <v>9</v>
       </c>
-      <c r="J8" t="s">
+      <c r="J8" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="K8" t="s">
-        <v>13</v>
+      <c r="K8" s="5" t="s">
+        <v>21</v>
       </c>
       <c r="L8" t="s">
         <v>3</v>
@@ -523,9 +623,10 @@
       <c r="I9" t="s">
         <v>11</v>
       </c>
-      <c r="K9" t="s">
-        <v>18</v>
-      </c>
+      <c r="J9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="5"/>
       <c r="L9" t="s">
         <v>7</v>
       </c>
@@ -535,19 +636,27 @@
         <v>1</v>
       </c>
       <c r="H10" t="s">
+        <v>19</v>
+      </c>
+      <c r="I10" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="4"/>
+      <c r="K10" s="5"/>
+      <c r="L10" t="s">
         <v>20</v>
-      </c>
-      <c r="I10" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="11" spans="6:12" x14ac:dyDescent="0.2">
       <c r="G11" t="s">
         <v>2</v>
       </c>
+      <c r="J11" s="4"/>
+      <c r="K11" s="5"/>
+    </row>
+    <row r="12" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="J12" s="4"/>
+      <c r="K12" s="5"/>
     </row>
     <row r="13" spans="6:12" x14ac:dyDescent="0.2">
       <c r="F13" t="s">
@@ -557,45 +666,142 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
+        <v>14</v>
+      </c>
+      <c r="I13" t="s">
+        <v>13</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" s="5"/>
+      <c r="L13" t="s">
         <v>15</v>
-      </c>
-      <c r="I13" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" t="s">
-        <v>17</v>
-      </c>
-      <c r="L13" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="14" spans="6:12" x14ac:dyDescent="0.2">
       <c r="G14" t="s">
         <v>1</v>
       </c>
+      <c r="J14" s="4"/>
+      <c r="K14" s="5"/>
     </row>
     <row r="15" spans="6:12" x14ac:dyDescent="0.2">
       <c r="G15" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="J15" s="4"/>
+      <c r="K15" s="5"/>
+    </row>
+    <row r="16" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="J16" s="4"/>
+      <c r="K16" s="5"/>
+    </row>
+    <row r="17" spans="6:12" x14ac:dyDescent="0.2">
       <c r="F17" t="s">
         <v>6</v>
       </c>
       <c r="G17" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="H17" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="I17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J17" s="4"/>
+      <c r="K17" s="5"/>
+      <c r="L17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="6:12" x14ac:dyDescent="0.2">
       <c r="G18" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="6:7" x14ac:dyDescent="0.2">
+      <c r="H18" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I18" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="J18" s="9"/>
+      <c r="K18" s="10"/>
+      <c r="L18" s="6" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="6:12" x14ac:dyDescent="0.2">
       <c r="G19" t="s">
         <v>2</v>
       </c>
+      <c r="J19" s="4"/>
+      <c r="K19" s="5"/>
+    </row>
+    <row r="20" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="F21" t="s">
+        <v>26</v>
+      </c>
+      <c r="G21" t="s">
+        <v>0</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="J21" s="7"/>
+      <c r="K21" s="8"/>
+      <c r="L21" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="22" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="G22" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="2"/>
+    </row>
+    <row r="23" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="G23" t="s">
+        <v>2</v>
+      </c>
+      <c r="J23" s="2"/>
+    </row>
+    <row r="25" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="F25" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" t="s">
+        <v>0</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" s="7"/>
+      <c r="K25" s="8"/>
+      <c r="L25" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="26" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="G26" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="6:12" x14ac:dyDescent="0.2">
+      <c r="G27" t="s">
+        <v>2</v>
+      </c>
+      <c r="J27" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
